--- a/artfynd/A 2666-2024 artfynd.xlsx
+++ b/artfynd/A 2666-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120189967</v>
+        <v>120189960</v>
       </c>
       <c r="B2" t="n">
-        <v>74629</v>
+        <v>78689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>492</v>
+        <v>1249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449355</v>
+        <v>449295</v>
       </c>
       <c r="R2" t="n">
-        <v>7169707</v>
+        <v>7169658</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120189960</v>
+        <v>120189967</v>
       </c>
       <c r="B3" t="n">
-        <v>78689</v>
+        <v>74629</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1249</v>
+        <v>492</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449295</v>
+        <v>449355</v>
       </c>
       <c r="R3" t="n">
-        <v>7169658</v>
+        <v>7169707</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 2666-2024 artfynd.xlsx
+++ b/artfynd/A 2666-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120189960</v>
       </c>
       <c r="B2" t="n">
-        <v>78689</v>
+        <v>78705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>120189967</v>
       </c>
       <c r="B3" t="n">
-        <v>74629</v>
+        <v>74645</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2666-2024 artfynd.xlsx
+++ b/artfynd/A 2666-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120189960</v>
+        <v>120189967</v>
       </c>
       <c r="B2" t="n">
-        <v>78705</v>
+        <v>74645</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1249</v>
+        <v>492</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449295</v>
+        <v>449355</v>
       </c>
       <c r="R2" t="n">
-        <v>7169658</v>
+        <v>7169707</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120189967</v>
+        <v>120189960</v>
       </c>
       <c r="B3" t="n">
-        <v>74645</v>
+        <v>78705</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>492</v>
+        <v>1249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449355</v>
+        <v>449295</v>
       </c>
       <c r="R3" t="n">
-        <v>7169707</v>
+        <v>7169658</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 2666-2024 artfynd.xlsx
+++ b/artfynd/A 2666-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120189967</v>
+        <v>120189960</v>
       </c>
       <c r="B2" t="n">
-        <v>74645</v>
+        <v>78705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>492</v>
+        <v>1249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449355</v>
+        <v>449295</v>
       </c>
       <c r="R2" t="n">
-        <v>7169707</v>
+        <v>7169658</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120189960</v>
+        <v>120189967</v>
       </c>
       <c r="B3" t="n">
-        <v>78705</v>
+        <v>74645</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1249</v>
+        <v>492</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449295</v>
+        <v>449355</v>
       </c>
       <c r="R3" t="n">
-        <v>7169658</v>
+        <v>7169707</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
